--- a/artfynd/A 31387-2026 artfynd.xlsx
+++ b/artfynd/A 31387-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY80"/>
+  <dimension ref="A1:AZ80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495505</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495501</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495494</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495509</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495516</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495522</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495500</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495502</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495512</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495520</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495521</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495484</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495493</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495499</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495518</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495523</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495513</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495511</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2520,6 +2615,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495490</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2627,6 +2727,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495495</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2729,6 +2834,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495497</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2831,6 +2941,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495504</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2928,6 +3043,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495525</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3035,6 +3155,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495526</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3132,6 +3257,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495503</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3237,6 +3367,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495487</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3334,6 +3469,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495488</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3431,6 +3571,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495491</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3528,6 +3673,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495496</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3625,6 +3775,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495498</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3722,6 +3877,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495506</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3819,6 +3979,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495508</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3916,6 +4081,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495510</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4013,6 +4183,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495515</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4110,6 +4285,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495517</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4207,6 +4387,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495519</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4304,6 +4489,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495524</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4401,6 +4591,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495489</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4498,6 +4693,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495492</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4595,6 +4795,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495442</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4692,6 +4897,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495482</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4789,6 +4999,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495486</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4886,6 +5101,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495449</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4983,6 +5203,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495470</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5080,6 +5305,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495479</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5177,6 +5407,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495448</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5274,6 +5509,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495453</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5371,6 +5611,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495447</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5468,6 +5713,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495446</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5565,6 +5815,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495450</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5662,6 +5917,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495455</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5759,6 +6019,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495459</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5856,6 +6121,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495468</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5953,6 +6223,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495456</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6050,6 +6325,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495460</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6147,6 +6427,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495483</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6244,6 +6529,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495480</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6346,6 +6636,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495445</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6448,6 +6743,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495451</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6555,6 +6855,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495452</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6657,6 +6962,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495462</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6759,6 +7069,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495463</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6866,6 +7181,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495473</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6968,6 +7288,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495474</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7070,6 +7395,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495475</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7167,6 +7497,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495461</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7264,6 +7599,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495454</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7361,6 +7701,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495469</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7458,6 +7803,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495443</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7555,6 +7905,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495457</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7652,6 +8007,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495458</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7749,6 +8109,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495465</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7846,6 +8211,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495466</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7943,6 +8313,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495471</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8040,6 +8415,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495472</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8137,6 +8517,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495476</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8234,6 +8619,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495478</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8331,6 +8721,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495481</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8428,8 +8823,94 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495464</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 31387-2026 artfynd.xlsx
+++ b/artfynd/A 31387-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135495505</v>
       </c>
       <c r="B2" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135495501</v>
       </c>
       <c r="B3" t="n">
-        <v>89354</v>
+        <v>89396</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135495494</v>
       </c>
       <c r="B4" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135495509</v>
       </c>
       <c r="B5" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135495516</v>
       </c>
       <c r="B6" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135495522</v>
       </c>
       <c r="B7" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135495500</v>
       </c>
       <c r="B8" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135495502</v>
       </c>
       <c r="B9" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135495512</v>
       </c>
       <c r="B10" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135495520</v>
       </c>
       <c r="B11" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135495521</v>
       </c>
       <c r="B12" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>135495484</v>
       </c>
       <c r="B13" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>135495493</v>
       </c>
       <c r="B14" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135495499</v>
       </c>
       <c r="B15" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135495518</v>
       </c>
       <c r="B16" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>135495523</v>
       </c>
       <c r="B17" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>135495513</v>
       </c>
       <c r="B18" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>135495511</v>
       </c>
       <c r="B19" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>135495490</v>
       </c>
       <c r="B20" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>135495495</v>
       </c>
       <c r="B21" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>135495497</v>
       </c>
       <c r="B22" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>135495504</v>
       </c>
       <c r="B23" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>135495525</v>
       </c>
       <c r="B24" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>135495526</v>
       </c>
       <c r="B25" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>135495487</v>
       </c>
       <c r="B27" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>135495488</v>
       </c>
       <c r="B28" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>135495491</v>
       </c>
       <c r="B29" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>135495496</v>
       </c>
       <c r="B30" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>135495498</v>
       </c>
       <c r="B31" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>135495506</v>
       </c>
       <c r="B32" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>135495508</v>
       </c>
       <c r="B33" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>135495510</v>
       </c>
       <c r="B34" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>135495515</v>
       </c>
       <c r="B35" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>135495517</v>
       </c>
       <c r="B36" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>135495519</v>
       </c>
       <c r="B37" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>135495524</v>
       </c>
       <c r="B38" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>135495489</v>
       </c>
       <c r="B39" t="n">
-        <v>106324</v>
+        <v>106379</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>135495492</v>
       </c>
       <c r="B40" t="n">
-        <v>106324</v>
+        <v>106379</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>135495442</v>
       </c>
       <c r="B41" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>135495482</v>
       </c>
       <c r="B42" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>135495486</v>
       </c>
       <c r="B43" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>135495449</v>
       </c>
       <c r="B44" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>135495470</v>
       </c>
       <c r="B45" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
         <v>135495479</v>
       </c>
       <c r="B46" t="n">
-        <v>92559</v>
+        <v>92601</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>135495448</v>
       </c>
       <c r="B47" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>135495453</v>
       </c>
       <c r="B48" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>135495447</v>
       </c>
       <c r="B49" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5622,7 +5622,7 @@
         <v>135495446</v>
       </c>
       <c r="B50" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>135495450</v>
       </c>
       <c r="B51" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>135495455</v>
       </c>
       <c r="B52" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>135495459</v>
       </c>
       <c r="B53" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>135495468</v>
       </c>
       <c r="B54" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>135495456</v>
       </c>
       <c r="B55" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>135495460</v>
       </c>
       <c r="B56" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>135495483</v>
       </c>
       <c r="B57" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>135495480</v>
       </c>
       <c r="B58" t="n">
-        <v>75468</v>
+        <v>75504</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>135495445</v>
       </c>
       <c r="B59" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>135495451</v>
       </c>
       <c r="B60" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>135495452</v>
       </c>
       <c r="B61" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>135495462</v>
       </c>
       <c r="B62" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>135495463</v>
       </c>
       <c r="B63" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>135495473</v>
       </c>
       <c r="B64" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         <v>135495461</v>
       </c>
       <c r="B67" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>135495454</v>
       </c>
       <c r="B68" t="n">
-        <v>99230</v>
+        <v>99277</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>135495469</v>
       </c>
       <c r="B69" t="n">
-        <v>99230</v>
+        <v>99277</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>135495443</v>
       </c>
       <c r="B70" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>135495457</v>
       </c>
       <c r="B71" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>135495458</v>
       </c>
       <c r="B72" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>135495465</v>
       </c>
       <c r="B73" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>135495466</v>
       </c>
       <c r="B74" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>135495471</v>
       </c>
       <c r="B75" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>135495472</v>
       </c>
       <c r="B76" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>135495476</v>
       </c>
       <c r="B77" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>135495478</v>
       </c>
       <c r="B78" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>135495481</v>
       </c>
       <c r="B79" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>135495464</v>
       </c>
       <c r="B80" t="n">
-        <v>106324</v>
+        <v>106379</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>

--- a/artfynd/A 31387-2026 artfynd.xlsx
+++ b/artfynd/A 31387-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135495505</v>
       </c>
       <c r="B2" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135495501</v>
       </c>
       <c r="B3" t="n">
-        <v>89396</v>
+        <v>89423</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135495494</v>
       </c>
       <c r="B4" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135495509</v>
       </c>
       <c r="B5" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135495516</v>
       </c>
       <c r="B6" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135495522</v>
       </c>
       <c r="B7" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135495500</v>
       </c>
       <c r="B8" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135495502</v>
       </c>
       <c r="B9" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135495512</v>
       </c>
       <c r="B10" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135495520</v>
       </c>
       <c r="B11" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135495521</v>
       </c>
       <c r="B12" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>135495484</v>
       </c>
       <c r="B13" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>135495493</v>
       </c>
       <c r="B14" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135495499</v>
       </c>
       <c r="B15" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135495518</v>
       </c>
       <c r="B16" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>135495523</v>
       </c>
       <c r="B17" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>135495513</v>
       </c>
       <c r="B18" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>135495511</v>
       </c>
       <c r="B19" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>135495488</v>
       </c>
       <c r="B28" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>135495491</v>
       </c>
       <c r="B29" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>135495496</v>
       </c>
       <c r="B30" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>135495498</v>
       </c>
       <c r="B31" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>135495506</v>
       </c>
       <c r="B32" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>135495508</v>
       </c>
       <c r="B33" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>135495510</v>
       </c>
       <c r="B34" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>135495515</v>
       </c>
       <c r="B35" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>135495517</v>
       </c>
       <c r="B36" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>135495519</v>
       </c>
       <c r="B37" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>135495524</v>
       </c>
       <c r="B38" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>135495489</v>
       </c>
       <c r="B39" t="n">
-        <v>106379</v>
+        <v>106406</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>135495492</v>
       </c>
       <c r="B40" t="n">
-        <v>106379</v>
+        <v>106406</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>135495442</v>
       </c>
       <c r="B41" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>135495482</v>
       </c>
       <c r="B42" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>135495486</v>
       </c>
       <c r="B43" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>135495449</v>
       </c>
       <c r="B44" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>135495470</v>
       </c>
       <c r="B45" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
         <v>135495479</v>
       </c>
       <c r="B46" t="n">
-        <v>92601</v>
+        <v>92628</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>135495448</v>
       </c>
       <c r="B47" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>135495453</v>
       </c>
       <c r="B48" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>135495447</v>
       </c>
       <c r="B49" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5622,7 +5622,7 @@
         <v>135495446</v>
       </c>
       <c r="B50" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>135495450</v>
       </c>
       <c r="B51" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>135495455</v>
       </c>
       <c r="B52" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>135495459</v>
       </c>
       <c r="B53" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>135495468</v>
       </c>
       <c r="B54" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>135495456</v>
       </c>
       <c r="B55" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>135495460</v>
       </c>
       <c r="B56" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>135495483</v>
       </c>
       <c r="B57" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>135495480</v>
       </c>
       <c r="B58" t="n">
-        <v>75504</v>
+        <v>75531</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         <v>135495461</v>
       </c>
       <c r="B67" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>135495454</v>
       </c>
       <c r="B68" t="n">
-        <v>99277</v>
+        <v>99304</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>135495469</v>
       </c>
       <c r="B69" t="n">
-        <v>99277</v>
+        <v>99304</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>135495443</v>
       </c>
       <c r="B70" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>135495457</v>
       </c>
       <c r="B71" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>135495458</v>
       </c>
       <c r="B72" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>135495465</v>
       </c>
       <c r="B73" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>135495466</v>
       </c>
       <c r="B74" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>135495471</v>
       </c>
       <c r="B75" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>135495472</v>
       </c>
       <c r="B76" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>135495476</v>
       </c>
       <c r="B77" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>135495478</v>
       </c>
       <c r="B78" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>135495481</v>
       </c>
       <c r="B79" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>135495464</v>
       </c>
       <c r="B80" t="n">
-        <v>106379</v>
+        <v>106406</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>

--- a/artfynd/A 31387-2026 artfynd.xlsx
+++ b/artfynd/A 31387-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135495501</v>
       </c>
       <c r="B3" t="n">
-        <v>89426</v>
+        <v>89428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135495494</v>
       </c>
       <c r="B4" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135495509</v>
       </c>
       <c r="B5" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135495516</v>
       </c>
       <c r="B6" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135495522</v>
       </c>
       <c r="B7" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135495500</v>
       </c>
       <c r="B8" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135495502</v>
       </c>
       <c r="B9" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135495512</v>
       </c>
       <c r="B10" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135495520</v>
       </c>
       <c r="B11" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135495521</v>
       </c>
       <c r="B12" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>135495484</v>
       </c>
       <c r="B13" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>135495493</v>
       </c>
       <c r="B14" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135495499</v>
       </c>
       <c r="B15" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135495518</v>
       </c>
       <c r="B16" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>135495523</v>
       </c>
       <c r="B17" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>135495488</v>
       </c>
       <c r="B28" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>135495491</v>
       </c>
       <c r="B29" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>135495496</v>
       </c>
       <c r="B30" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>135495498</v>
       </c>
       <c r="B31" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>135495506</v>
       </c>
       <c r="B32" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>135495508</v>
       </c>
       <c r="B33" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>135495510</v>
       </c>
       <c r="B34" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>135495515</v>
       </c>
       <c r="B35" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>135495517</v>
       </c>
       <c r="B36" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>135495519</v>
       </c>
       <c r="B37" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>135495524</v>
       </c>
       <c r="B38" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>135495489</v>
       </c>
       <c r="B39" t="n">
-        <v>106411</v>
+        <v>106413</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>135495492</v>
       </c>
       <c r="B40" t="n">
-        <v>106411</v>
+        <v>106413</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>135495442</v>
       </c>
       <c r="B41" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>135495482</v>
       </c>
       <c r="B42" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>135495486</v>
       </c>
       <c r="B43" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
         <v>135495479</v>
       </c>
       <c r="B46" t="n">
-        <v>92633</v>
+        <v>92635</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>135495448</v>
       </c>
       <c r="B47" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>135495453</v>
       </c>
       <c r="B48" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>135495447</v>
       </c>
       <c r="B49" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5622,7 +5622,7 @@
         <v>135495446</v>
       </c>
       <c r="B50" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>135495450</v>
       </c>
       <c r="B51" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>135495455</v>
       </c>
       <c r="B52" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>135495459</v>
       </c>
       <c r="B53" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>135495468</v>
       </c>
       <c r="B54" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         <v>135495461</v>
       </c>
       <c r="B67" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>135495454</v>
       </c>
       <c r="B68" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>135495469</v>
       </c>
       <c r="B69" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>135495443</v>
       </c>
       <c r="B70" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>135495457</v>
       </c>
       <c r="B71" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>135495458</v>
       </c>
       <c r="B72" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>135495465</v>
       </c>
       <c r="B73" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>135495466</v>
       </c>
       <c r="B74" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>135495471</v>
       </c>
       <c r="B75" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>135495472</v>
       </c>
       <c r="B76" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>135495476</v>
       </c>
       <c r="B77" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>135495478</v>
       </c>
       <c r="B78" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>135495481</v>
       </c>
       <c r="B79" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>135495464</v>
       </c>
       <c r="B80" t="n">
-        <v>106411</v>
+        <v>106413</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>

--- a/artfynd/A 31387-2026 artfynd.xlsx
+++ b/artfynd/A 31387-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135495505</v>
       </c>
       <c r="B2" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135495501</v>
       </c>
       <c r="B3" t="n">
-        <v>89428</v>
+        <v>89430</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135495494</v>
       </c>
       <c r="B4" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135495509</v>
       </c>
       <c r="B5" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135495516</v>
       </c>
       <c r="B6" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135495522</v>
       </c>
       <c r="B7" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135495500</v>
       </c>
       <c r="B8" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135495502</v>
       </c>
       <c r="B9" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135495512</v>
       </c>
       <c r="B10" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135495520</v>
       </c>
       <c r="B11" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135495521</v>
       </c>
       <c r="B12" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>135495484</v>
       </c>
       <c r="B13" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>135495493</v>
       </c>
       <c r="B14" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135495499</v>
       </c>
       <c r="B15" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135495518</v>
       </c>
       <c r="B16" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>135495523</v>
       </c>
       <c r="B17" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>135495513</v>
       </c>
       <c r="B18" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>135495511</v>
       </c>
       <c r="B19" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>135495490</v>
       </c>
       <c r="B20" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>135495495</v>
       </c>
       <c r="B21" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>135495497</v>
       </c>
       <c r="B22" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>135495504</v>
       </c>
       <c r="B23" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>135495525</v>
       </c>
       <c r="B24" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>135495526</v>
       </c>
       <c r="B25" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>135495503</v>
       </c>
       <c r="B26" t="n">
-        <v>4776</v>
+        <v>4777</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>135495487</v>
       </c>
       <c r="B27" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>135495488</v>
       </c>
       <c r="B28" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>135495491</v>
       </c>
       <c r="B29" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>135495496</v>
       </c>
       <c r="B30" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>135495498</v>
       </c>
       <c r="B31" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>135495506</v>
       </c>
       <c r="B32" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>135495508</v>
       </c>
       <c r="B33" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>135495510</v>
       </c>
       <c r="B34" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>135495515</v>
       </c>
       <c r="B35" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>135495517</v>
       </c>
       <c r="B36" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>135495519</v>
       </c>
       <c r="B37" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>135495524</v>
       </c>
       <c r="B38" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>135495489</v>
       </c>
       <c r="B39" t="n">
-        <v>106413</v>
+        <v>106433</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>135495492</v>
       </c>
       <c r="B40" t="n">
-        <v>106413</v>
+        <v>106433</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>135495442</v>
       </c>
       <c r="B41" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>135495482</v>
       </c>
       <c r="B42" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>135495486</v>
       </c>
       <c r="B43" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>135495449</v>
       </c>
       <c r="B44" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>135495470</v>
       </c>
       <c r="B45" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
         <v>135495479</v>
       </c>
       <c r="B46" t="n">
-        <v>92635</v>
+        <v>92650</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>135495448</v>
       </c>
       <c r="B47" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>135495453</v>
       </c>
       <c r="B48" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>135495447</v>
       </c>
       <c r="B49" t="n">
-        <v>92064</v>
+        <v>92078</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5622,7 +5622,7 @@
         <v>135495446</v>
       </c>
       <c r="B50" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>135495450</v>
       </c>
       <c r="B51" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>135495455</v>
       </c>
       <c r="B52" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>135495459</v>
       </c>
       <c r="B53" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>135495468</v>
       </c>
       <c r="B54" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>135495456</v>
       </c>
       <c r="B55" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>135495460</v>
       </c>
       <c r="B56" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>135495483</v>
       </c>
       <c r="B57" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>135495480</v>
       </c>
       <c r="B58" t="n">
-        <v>75531</v>
+        <v>75533</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>135495445</v>
       </c>
       <c r="B59" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>135495451</v>
       </c>
       <c r="B60" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>135495452</v>
       </c>
       <c r="B61" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>135495462</v>
       </c>
       <c r="B62" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>135495463</v>
       </c>
       <c r="B63" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>135495473</v>
       </c>
       <c r="B64" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         <v>135495474</v>
       </c>
       <c r="B65" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         <v>135495475</v>
       </c>
       <c r="B66" t="n">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         <v>135495461</v>
       </c>
       <c r="B67" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>135495454</v>
       </c>
       <c r="B68" t="n">
-        <v>99311</v>
+        <v>99328</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>135495469</v>
       </c>
       <c r="B69" t="n">
-        <v>99311</v>
+        <v>99328</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>135495443</v>
       </c>
       <c r="B70" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>135495457</v>
       </c>
       <c r="B71" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>135495458</v>
       </c>
       <c r="B72" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>135495465</v>
       </c>
       <c r="B73" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>135495466</v>
       </c>
       <c r="B74" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>135495471</v>
       </c>
       <c r="B75" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>135495472</v>
       </c>
       <c r="B76" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>135495476</v>
       </c>
       <c r="B77" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>135495478</v>
       </c>
       <c r="B78" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>135495481</v>
       </c>
       <c r="B79" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>135495464</v>
       </c>
       <c r="B80" t="n">
-        <v>106413</v>
+        <v>106433</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>

--- a/artfynd/A 31387-2026 artfynd.xlsx
+++ b/artfynd/A 31387-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135495505</v>
       </c>
       <c r="B2" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135495501</v>
       </c>
       <c r="B3" t="n">
-        <v>89430</v>
+        <v>89431</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135495494</v>
       </c>
       <c r="B4" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135495509</v>
       </c>
       <c r="B5" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135495516</v>
       </c>
       <c r="B6" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135495522</v>
       </c>
       <c r="B7" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135495500</v>
       </c>
       <c r="B8" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135495502</v>
       </c>
       <c r="B9" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135495512</v>
       </c>
       <c r="B10" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135495520</v>
       </c>
       <c r="B11" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135495521</v>
       </c>
       <c r="B12" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>135495484</v>
       </c>
       <c r="B13" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>135495493</v>
       </c>
       <c r="B14" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135495499</v>
       </c>
       <c r="B15" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135495518</v>
       </c>
       <c r="B16" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>135495523</v>
       </c>
       <c r="B17" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>135495513</v>
       </c>
       <c r="B18" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>135495511</v>
       </c>
       <c r="B19" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>135495488</v>
       </c>
       <c r="B28" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>135495491</v>
       </c>
       <c r="B29" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>135495496</v>
       </c>
       <c r="B30" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>135495498</v>
       </c>
       <c r="B31" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>135495506</v>
       </c>
       <c r="B32" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>135495508</v>
       </c>
       <c r="B33" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>135495510</v>
       </c>
       <c r="B34" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>135495515</v>
       </c>
       <c r="B35" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>135495517</v>
       </c>
       <c r="B36" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>135495519</v>
       </c>
       <c r="B37" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>135495524</v>
       </c>
       <c r="B38" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>135495489</v>
       </c>
       <c r="B39" t="n">
-        <v>106433</v>
+        <v>106435</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>135495492</v>
       </c>
       <c r="B40" t="n">
-        <v>106433</v>
+        <v>106435</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>135495442</v>
       </c>
       <c r="B41" t="n">
-        <v>97530</v>
+        <v>97531</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>135495482</v>
       </c>
       <c r="B42" t="n">
-        <v>97530</v>
+        <v>97531</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>135495486</v>
       </c>
       <c r="B43" t="n">
-        <v>97530</v>
+        <v>97531</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>135495449</v>
       </c>
       <c r="B44" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>135495470</v>
       </c>
       <c r="B45" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
         <v>135495479</v>
       </c>
       <c r="B46" t="n">
-        <v>92650</v>
+        <v>92651</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>135495448</v>
       </c>
       <c r="B47" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>135495453</v>
       </c>
       <c r="B48" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>135495447</v>
       </c>
       <c r="B49" t="n">
-        <v>92078</v>
+        <v>92079</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5622,7 +5622,7 @@
         <v>135495446</v>
       </c>
       <c r="B50" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>135495450</v>
       </c>
       <c r="B51" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>135495455</v>
       </c>
       <c r="B52" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>135495459</v>
       </c>
       <c r="B53" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>135495468</v>
       </c>
       <c r="B54" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>135495456</v>
       </c>
       <c r="B55" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>135495460</v>
       </c>
       <c r="B56" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>135495483</v>
       </c>
       <c r="B57" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>135495480</v>
       </c>
       <c r="B58" t="n">
-        <v>75533</v>
+        <v>75534</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         <v>135495461</v>
       </c>
       <c r="B67" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>135495454</v>
       </c>
       <c r="B68" t="n">
-        <v>99328</v>
+        <v>99329</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>135495469</v>
       </c>
       <c r="B69" t="n">
-        <v>99328</v>
+        <v>99329</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>135495443</v>
       </c>
       <c r="B70" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>135495457</v>
       </c>
       <c r="B71" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>135495458</v>
       </c>
       <c r="B72" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>135495465</v>
       </c>
       <c r="B73" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>135495466</v>
       </c>
       <c r="B74" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>135495471</v>
       </c>
       <c r="B75" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>135495472</v>
       </c>
       <c r="B76" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>135495476</v>
       </c>
       <c r="B77" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>135495478</v>
       </c>
       <c r="B78" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>135495481</v>
       </c>
       <c r="B79" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>135495464</v>
       </c>
       <c r="B80" t="n">
-        <v>106433</v>
+        <v>106435</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
